--- a/forms/trg/Formulir_TRG_mrcrg.xlsx
+++ b/forms/trg/Formulir_TRG_mrcrg.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
